--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484302_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484302_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5404</v>
+        <v>7.9647</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7737</v>
+        <v>8.4704</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2333</v>
+        <v>-0.5057</v>
       </c>
       <c r="G2" t="n">
         <v>7.4679</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3813</v>
+        <v>2.8057</v>
       </c>
       <c r="T2" t="n">
-        <v>2.226</v>
+        <v>1.9226</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1554</v>
+        <v>0.883</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9414</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7223</v>
+        <v>4.6129</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9407</v>
+        <v>1.7496</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7816</v>
+        <v>2.8633</v>
       </c>
       <c r="G3" t="n">
         <v>1.8983</v>
@@ -688,13 +688,13 @@
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8826000000000001</v>
+        <v>1.7732</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5614</v>
+        <v>1.3703</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3212</v>
+        <v>0.4029</v>
       </c>
       <c r="V3" t="n">
         <v>0.9414</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.868</v>
+        <v>2.5411</v>
       </c>
       <c r="E4" t="n">
         <v>0.0322</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8357</v>
+        <v>2.5089</v>
       </c>
       <c r="G4" t="n">
         <v>2.0135</v>
@@ -766,13 +766,13 @@
         <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1084</v>
+        <v>2.7815</v>
       </c>
       <c r="T4" t="n">
         <v>1.7472</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3611</v>
+        <v>1.0343</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8865</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.189</v>
+        <v>1.7102</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2778</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9112</v>
+        <v>1.1291</v>
       </c>
       <c r="G5" t="n">
         <v>0.6374</v>
@@ -844,13 +844,13 @@
         <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1711</v>
+        <v>0.3501</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.2236</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0914</v>
+        <v>0.1265</v>
       </c>
       <c r="V5" t="n">
         <v>0.3321</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6621</v>
+        <v>0.4173</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5733</v>
+        <v>0.8655</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9112</v>
+        <v>-0.4482</v>
       </c>
       <c r="G6" t="n">
         <v>-1.252</v>
@@ -922,13 +922,13 @@
         <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>2.73</v>
+        <v>2.4852</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7928</v>
+        <v>2.085</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06279999999999999</v>
+        <v>0.4002</v>
       </c>
       <c r="V6" t="n">
         <v>-2.7693</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0179</v>
+        <v>-0.1425</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9402</v>
+        <v>-2.738</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9223</v>
+        <v>2.5954</v>
       </c>
       <c r="G7" t="n">
         <v>1.4097</v>
@@ -1000,13 +1000,13 @@
         <v>2.5395</v>
       </c>
       <c r="S7" t="n">
-        <v>3.0149</v>
+        <v>2.8903</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8629</v>
+        <v>2.0651</v>
       </c>
       <c r="U7" t="n">
-        <v>1.152</v>
+        <v>0.8252</v>
       </c>
       <c r="V7" t="n">
         <v>0.8317</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2904</v>
+        <v>-2.1459</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8577</v>
+        <v>0.9477</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1481</v>
+        <v>-3.0936</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8531</v>
@@ -1078,13 +1078,13 @@
         <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0819</v>
+        <v>0.2263</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4914</v>
+        <v>0.5813</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4095</v>
+        <v>-0.355</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4959</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5099</v>
+        <v>-3.2065</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3647</v>
+        <v>-3.0613</v>
       </c>
       <c r="F9" t="n">
         <v>-0.1452</v>
@@ -1156,10 +1156,10 @@
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3302</v>
+        <v>0.6335</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3385</v>
+        <v>0.6419</v>
       </c>
       <c r="U9" t="n">
         <v>-0.0083</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2417</v>
+        <v>-3.8295</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3139</v>
+        <v>-1.0106</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9278</v>
+        <v>-2.8189</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2033</v>
@@ -1234,13 +1234,13 @@
         <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5464</v>
+        <v>-0.1341</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1402</v>
+        <v>0.1631</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4061</v>
+        <v>-0.2972</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2735</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.921900000000001</v>
+        <v>7.921800000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>5.8366</v>
+        <v>5.836599999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0852</v>
+        <v>2.0851</v>
       </c>
       <c r="G11" t="n">
         <v>2.095000000000001</v>
@@ -1312,10 +1312,10 @@
         <v>15.6273</v>
       </c>
       <c r="S11" t="n">
-        <v>13.8118</v>
+        <v>13.8117</v>
       </c>
       <c r="T11" t="n">
-        <v>10.8003</v>
+        <v>10.8001</v>
       </c>
       <c r="U11" t="n">
         <v>3.0116</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.2412</v>
+        <v>7.7352</v>
       </c>
       <c r="E12" t="n">
-        <v>7.2775</v>
+        <v>7.5808</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0363</v>
+        <v>0.1543</v>
       </c>
       <c r="G12" t="n">
         <v>6.0405</v>
@@ -1390,13 +1390,13 @@
         <v>2.7348</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6077</v>
+        <v>-2.1137</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8803</v>
+        <v>-0.5769</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7274</v>
+        <v>-1.5368</v>
       </c>
       <c r="V12" t="n">
         <v>2.0503</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6334</v>
+        <v>2.9879</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2599</v>
+        <v>4.451</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6265</v>
+        <v>-1.4631</v>
       </c>
       <c r="G13" t="n">
         <v>1.4914</v>
@@ -1468,13 +1468,13 @@
         <v>3.1255</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4125</v>
+        <v>-2.058</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6027</v>
+        <v>-0.2062</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0152</v>
+        <v>-1.8518</v>
       </c>
       <c r="V13" t="n">
         <v>2.3824</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.8307</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.369</v>
+        <v>-0.6724</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3424</v>
+        <v>1.5031</v>
       </c>
       <c r="G14" t="n">
         <v>0.091</v>
@@ -1546,13 +1546,13 @@
         <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8953</v>
+        <v>-1.038</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0221</v>
+        <v>-0.2812</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9174</v>
+        <v>-0.7567</v>
       </c>
       <c r="V14" t="n">
         <v>0.9962</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3853</v>
+        <v>0.117</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0492</v>
+        <v>1.2403</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6639</v>
+        <v>-1.1233</v>
       </c>
       <c r="G15" t="n">
         <v>1.7372</v>
@@ -1624,13 +1624,13 @@
         <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>0.476</v>
+        <v>0.2078</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0594</v>
+        <v>0.2504</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5833</v>
+        <v>-0.0427</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8279</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6867</v>
+        <v>-0.4766</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3218</v>
+        <v>-0.2207</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3648</v>
+        <v>-0.2559</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0207</v>
@@ -1702,13 +1702,13 @@
         <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8298</v>
+        <v>-0.6197</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2283</v>
+        <v>-0.1272</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6015</v>
+        <v>-0.4925</v>
       </c>
       <c r="V16" t="n">
         <v>0.5545</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4649</v>
+        <v>-0.9283</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7571</v>
+        <v>1.1616</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2221</v>
+        <v>-2.0899</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4338</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3715</v>
+        <v>0.1651</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5915</v>
+        <v>-0.187</v>
       </c>
       <c r="U17" t="n">
-        <v>0.22</v>
+        <v>0.3521</v>
       </c>
       <c r="V17" t="n">
         <v>-1.441</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5959</v>
+        <v>-1.1348</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0082</v>
+        <v>-0.1707</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4123</v>
+        <v>-0.964</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4923</v>
+        <v>-0.7255</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2853</v>
+        <v>-1.3592</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.7775</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5984</v>
+        <v>0.1779</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3697</v>
+        <v>-0.591</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.968</v>
+        <v>0.7688</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8939</v>
+        <v>-0.9034</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0844</v>
+        <v>-0.7682</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8095</v>
+        <v>-0.1352</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8617</v>
+        <v>-0.4175</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4099</v>
+        <v>-0.3486</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4518</v>
+        <v>-0.0689</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.1638</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8426</v>
+        <v>-1.2109</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4741</v>
+        <v>-1.7049</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3685</v>
+        <v>0.494</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7255</v>
+        <v>-2.4923</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3592</v>
+        <v>0.2853</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6336000000000001</v>
+        <v>-2.7775</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1779</v>
+        <v>-1.5984</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.591</v>
+        <v>0.3697</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7688</v>
+        <v>-1.968</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9034</v>
+        <v>-0.8939</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7682</v>
+        <v>-0.0844</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1352</v>
+        <v>-0.8095</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1253</v>
+        <v>-0.4767</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.652</v>
+        <v>-0.1065</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4733</v>
+        <v>-0.3701</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1624</v>
+        <v>-1.7709</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2078</v>
+        <v>-2.0055</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0454</v>
+        <v>0.2347</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8685</v>
@@ -2014,13 +2014,13 @@
         <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2706</v>
+        <v>-0.879</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3961</v>
+        <v>-0.1939</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.6852</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7593</v>
+        <v>-2.5156</v>
       </c>
       <c r="E21" t="n">
         <v>-1.9526</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8067</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9061</v>
@@ -2092,13 +2092,13 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2672</v>
+        <v>-1.0235</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3961</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8711</v>
+        <v>-0.6274</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7572</v>
+        <v>-4.337</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8692</v>
+        <v>-4.7681</v>
       </c>
       <c r="F22" t="n">
-        <v>1.112</v>
+        <v>0.4311</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9444</v>
@@ -2170,13 +2170,13 @@
         <v>3.1255</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5822</v>
+        <v>-2.1619</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6849</v>
+        <v>-0.5838</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8972</v>
+        <v>-1.5781</v>
       </c>
       <c r="V22" t="n">
         <v>1.5507</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8861</v>
+        <v>-5.1963</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2263</v>
+        <v>-5.024</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.1723</v>
       </c>
       <c r="G23" t="n">
         <v>-2.064</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.064</v>
+        <v>-1.3743</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4566</v>
+        <v>-0.2544</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.6074</v>
+        <v>-1.1199</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.921900000000001</v>
+        <v>-5.899600000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.085300000000001</v>
+        <v>-2.085199999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.8365</v>
+        <v>-3.8143</v>
       </c>
       <c r="G24" t="n">
         <v>-2.095199999999999</v>
@@ -2326,13 +2326,13 @@
         <v>20.5111</v>
       </c>
       <c r="S24" t="n">
-        <v>-13.8118</v>
+        <v>-11.7894</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.0115</v>
+        <v>-3.0114</v>
       </c>
       <c r="U24" t="n">
-        <v>-10.8001</v>
+        <v>-8.777999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>3.1014</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484302_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484302_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.3824</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,7 @@
       <c r="X11" t="n">
         <v>-8.588100000000001</v>
       </c>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1458,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,11 +1624,16 @@
       <c r="X14" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.117</v>
+        <v>0.607</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2403</v>
+        <v>0.607</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1233</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7372</v>
+        <v>0.607</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8524</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5896</v>
+        <v>0.607</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6307</v>
+        <v>0.607</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0409</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5898</v>
+        <v>0.607</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8935</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8933</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2078</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2504</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0427</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4766</v>
+        <v>0.607</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2207</v>
+        <v>0.607</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2559</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0207</v>
+        <v>0.607</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7885</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8091</v>
+        <v>0.607</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3287</v>
+        <v>0.607</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0028</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6741</v>
+        <v>0.607</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3494</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2144</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.135</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6197</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1272</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4925</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9283</v>
+        <v>0.117</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1616</v>
+        <v>1.2403</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0899</v>
+        <v>-1.1233</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4338</v>
+        <v>1.7372</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.596</v>
+        <v>-0.8524</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1623</v>
+        <v>2.5896</v>
       </c>
       <c r="J17" t="n">
-        <v>0.13</v>
+        <v>2.6307</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1023</v>
+        <v>0.0409</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0276</v>
+        <v>2.5898</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5638</v>
+        <v>-0.8935</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6984</v>
+        <v>-0.8933</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1346</v>
+        <v>-0.0002</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1651</v>
+        <v>0.2078</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.187</v>
+        <v>0.2504</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3521</v>
+        <v>-0.0427</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.441</v>
+        <v>-1.8279</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6596</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1348</v>
+        <v>-0.4766</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1707</v>
+        <v>-0.2207</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.964</v>
+        <v>-0.2559</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7255</v>
+        <v>-0.0207</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3592</v>
+        <v>0.7885</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6336000000000001</v>
+        <v>-0.8091</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1779</v>
+        <v>0.3287</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.591</v>
+        <v>1.0028</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7688</v>
+        <v>-0.6741</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9034</v>
+        <v>-0.3494</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7682</v>
+        <v>-0.2144</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1352</v>
+        <v>-0.135</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4175</v>
+        <v>-0.6197</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3486</v>
+        <v>-0.1272</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0689</v>
+        <v>-0.4925</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1638</v>
+        <v>0.5545</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2109</v>
+        <v>-0.9283</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7049</v>
+        <v>1.1616</v>
       </c>
       <c r="F19" t="n">
-        <v>0.494</v>
+        <v>-2.0899</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4923</v>
+        <v>-0.4338</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2853</v>
+        <v>-0.596</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7775</v>
+        <v>0.1623</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5984</v>
+        <v>0.13</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3697</v>
+        <v>0.1023</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.968</v>
+        <v>0.0276</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8939</v>
+        <v>-0.5638</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0844</v>
+        <v>-0.6984</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8095</v>
+        <v>0.1346</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4767</v>
+        <v>0.1651</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1065</v>
+        <v>-0.187</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3701</v>
+        <v>0.3521</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.441</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.6596</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7709</v>
+        <v>-1.7418</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0055</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2347</v>
+        <v>-0.964</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8685</v>
+        <v>-1.3325</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0614</v>
+        <v>-1.3592</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8071</v>
+        <v>0.0266</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8349</v>
+        <v>-0.4291</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4323</v>
+        <v>-0.591</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2673</v>
+        <v>0.1619</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0336</v>
+        <v>-0.9034</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4937</v>
+        <v>-0.7682</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5399</v>
+        <v>-0.1352</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.879</v>
+        <v>-0.4175</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1939</v>
+        <v>-0.3486</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6852</v>
+        <v>-0.0689</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.1638</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5156</v>
+        <v>-1.7709</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9526</v>
+        <v>-2.0055</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5629999999999999</v>
+        <v>0.2347</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9061</v>
+        <v>-1.8685</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2568</v>
+        <v>-0.0614</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3508</v>
+        <v>-1.8071</v>
       </c>
       <c r="J21" t="n">
-        <v>0.397</v>
+        <v>-0.8349</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2239</v>
+        <v>0.4323</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6208</v>
+        <v>-1.2673</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.303</v>
+        <v>-1.0336</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.033</v>
+        <v>-0.4937</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.27</v>
+        <v>-0.5399</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0235</v>
+        <v>-0.879</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3961</v>
+        <v>-0.1939</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6274</v>
+        <v>-0.6852</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2108,12 +2204,17 @@
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.337</v>
+        <v>-1.8178</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7681</v>
+        <v>-2.3119</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4311</v>
+        <v>0.494</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9444</v>
+        <v>-3.0993</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6493</v>
+        <v>0.2853</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2951</v>
+        <v>-3.3845</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.496</v>
+        <v>-2.2053</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5503</v>
+        <v>0.3697</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0543</v>
+        <v>-2.575</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4484</v>
+        <v>-0.8939</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.099</v>
+        <v>-0.0844</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3494</v>
+        <v>-0.8095</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1255</v>
+        <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1619</v>
+        <v>-0.4767</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5838</v>
+        <v>-0.1065</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.5781</v>
+        <v>-0.3701</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5507</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1963</v>
+        <v>-2.5156</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.024</v>
+        <v>-1.9526</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1723</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.064</v>
+        <v>-0.9061</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.702</v>
+        <v>-1.2568</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.362</v>
+        <v>0.3508</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8395</v>
+        <v>0.397</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6127</v>
+        <v>-0.2239</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2268</v>
+        <v>0.6208</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2245</v>
+        <v>-1.303</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0893</v>
+        <v>-1.033</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1352</v>
+        <v>-0.27</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7581</v>
+        <v>-0.586</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3743</v>
+        <v>-1.0235</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2544</v>
+        <v>-0.3961</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1199</v>
+        <v>-0.6274</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2264,12 +2370,17 @@
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.899600000000002</v>
+        <v>-4.337</v>
       </c>
       <c r="E24" t="n">
+        <v>-4.7681</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.9444</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.6493</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.2951</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.496</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.5503</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.4484</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.099</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.3494</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.1255</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-2.1619</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.5838</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-1.5781</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.5507</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A. VINALLONGA GOMEZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-5.1963</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5.024</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.1723</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.064</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.702</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.362</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.8395</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.6127</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.2268</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.2245</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.0893</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.1352</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-1.3743</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.2544</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-1.1199</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484302_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-5.899500000000001</v>
+      </c>
+      <c r="E26" t="n">
         <v>-2.085199999999999</v>
       </c>
-      <c r="F24" t="n">
-        <v>-3.8143</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="F26" t="n">
+        <v>-3.814299999999999</v>
+      </c>
+      <c r="G26" t="n">
         <v>-2.095199999999999</v>
       </c>
-      <c r="H24" t="n">
-        <v>2.623699999999999</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H26" t="n">
+        <v>2.623700000000001</v>
+      </c>
+      <c r="I26" t="n">
         <v>-4.7186</v>
       </c>
-      <c r="J24" t="n">
-        <v>7.9655</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6.610099999999997</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.355</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="J26" t="n">
+        <v>7.965600000000001</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6.610099999999999</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.3551</v>
+      </c>
+      <c r="M26" t="n">
         <v>-10.0606</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-3.9867</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>-6.0738</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>4.8837</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-15.6273</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>20.5111</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>-11.7894</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>-3.0114</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>-8.777999999999999</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>3.1014</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>8.588100000000001</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-5.486800000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
